--- a/test/POC1G/model_parsing_diagnostics.POC1G.xlsx
+++ b/test/POC1G/model_parsing_diagnostics.POC1G.xlsx
@@ -14,14 +14,14 @@
   </bookViews>
   <sheets>
     <sheet name="species_in_model" sheetId="1" r:id="rId1"/>
-    <sheet name="species_extra" r:id="rId5" sheetId="2"/>
-    <sheet name="elements_in_reactions" r:id="rId6" sheetId="3"/>
-    <sheet name="speciation" r:id="rId7" sheetId="4"/>
-    <sheet name="reaction_dependency" r:id="rId8" sheetId="5"/>
-    <sheet name="transport_parameters" r:id="rId9" sheetId="6"/>
-    <sheet name="reaction_parameters" r:id="rId10" sheetId="7"/>
+    <sheet name="species_extra" sheetId="2" r:id="rId5"/>
+    <sheet name="elements_in_reactions" sheetId="3" r:id="rId6"/>
+    <sheet name="speciation" sheetId="4" r:id="rId7"/>
+    <sheet name="reaction_dependency" sheetId="5" r:id="rId8"/>
+    <sheet name="transport_parameters" sheetId="6" r:id="rId9"/>
+    <sheet name="reaction_parameters" sheetId="7" r:id="rId10"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr fullCalcOnLoad="1" calcMode="auto"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="39">
   <si>
     <t>label</t>
   </si>
@@ -566,7 +566,7 @@
       <c r="I2" t="s">
         <v>17</v>
       </c>
-      <c r="J2">
+      <c r="J2" t="n">
         <v>1</v>
       </c>
       <c r="K2" t="s">
@@ -582,7 +582,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CAF0E20E-E4D8-9B45-9C94-E89B574F109C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DBEB6BD4-7B66-4D49-8EDC-D32F3AE5B38D}">
   <dimension ref="A1:B2"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
@@ -608,7 +608,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CAF0E20E-E4D8-9B45-9C94-E89B574F109C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{98E33B40-677E-409B-9433-118218E4161E}">
   <dimension ref="A1:C1"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
@@ -629,7 +629,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CAF0E20E-E4D8-9B45-9C94-E89B574F109C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2009F7A2-974E-4C41-B587-A5CAF56D61F2}">
   <dimension ref="A1:F1"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
@@ -659,7 +659,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CAF0E20E-E4D8-9B45-9C94-E89B574F109C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DC569031-4B78-4517-A491-8D9934248A8D}">
   <dimension ref="A1:B2"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
@@ -685,7 +685,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CAF0E20E-E4D8-9B45-9C94-E89B574F109C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{31391EC6-16C8-4D29-9E5C-D9BF8906051C}">
   <dimension ref="A1:B6"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
@@ -743,7 +743,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CAF0E20E-E4D8-9B45-9C94-E89B574F109C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BF4F1D68-5B4F-4BE7-AF06-040D49391D40}">
   <dimension ref="A1:C2"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
